--- a/artfynd/A 28160-2022 artfynd.xlsx
+++ b/artfynd/A 28160-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122101614</v>
       </c>
       <c r="B2" t="n">
-        <v>90755</v>
+        <v>90756</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28160-2022 artfynd.xlsx
+++ b/artfynd/A 28160-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122101614</v>
       </c>
       <c r="B2" t="n">
-        <v>90756</v>
+        <v>90765</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28160-2022 artfynd.xlsx
+++ b/artfynd/A 28160-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122101614</v>
       </c>
       <c r="B2" t="n">
-        <v>90765</v>
+        <v>90772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28160-2022 artfynd.xlsx
+++ b/artfynd/A 28160-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122101614</v>
       </c>
       <c r="B2" t="n">
-        <v>90790</v>
+        <v>90800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28160-2022 artfynd.xlsx
+++ b/artfynd/A 28160-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122101614</v>
       </c>
       <c r="B2" t="n">
-        <v>90800</v>
+        <v>90812</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28160-2022 artfynd.xlsx
+++ b/artfynd/A 28160-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122101614</v>
       </c>
       <c r="B2" t="n">
-        <v>90812</v>
+        <v>90819</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28160-2022 artfynd.xlsx
+++ b/artfynd/A 28160-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122101614</v>
       </c>
       <c r="B2" t="n">
-        <v>90819</v>
+        <v>90824</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>1205</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Stor aspticka</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Phellinus populicola</t>
@@ -770,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Enviro Planning, Sofia Berg, Anders Esplund</t>
+          <t>Anders Esplund, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 28160-2022 artfynd.xlsx
+++ b/artfynd/A 28160-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122101614</v>
       </c>
       <c r="B2" t="n">
-        <v>90824</v>
+        <v>90837</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>1205</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Phellinus populicola</t>
@@ -765,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg, Enviro Planning</t>
+          <t>Enviro Planning, Sofia Berg, Anders Esplund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
